--- a/Layout_Bajas.xlsx
+++ b/Layout_Bajas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout_Bajas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo Motivos Baja" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Layout_Bajas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catálogo Motivos Baja" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -539,6 +539,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -581,6 +582,11 @@
           <t>CONTROL</t>
         </is>
       </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>PLAZA</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -655,6 +661,12 @@
 Determinante</t>
         </is>
       </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>ID_PLAZA
+Plaza a Liberar</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -717,6 +729,11 @@
           <t>Núm. o NULL</t>
         </is>
       </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Ej: 41471</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -773,6 +790,11 @@
       <c r="L6" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>50694</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -831,6 +853,11 @@
           <t>NULL</t>
         </is>
       </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -887,14 +914,19 @@
       <c r="L8" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>67890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A3"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
